--- a/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>保険医療機関番号７桁。Identifier型の拡張  
-「InsuranceOrganizationNo」を使用する。systemには医療機関コードを表すOID「1.2.392.100495.20.3.23」を指定する。  
+「InsuranceOrganizationNo」を使用する。systemには医療機関コードを表すOID「$JP_IdSystem_MedicalOrganizationID」を指定する。  
 「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」の定義をベースにしているが、URLを以下に変更している  
 http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationNo</t>
   </si>
@@ -459,7 +459,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.23</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicalOrganizationID</t>
   </si>
   <si>
     <t>Identifier.system</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -272,7 +272,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -353,7 +353,7 @@
     <t>拡張値の値 - データ型の制約付きセットの1つでなければなりません（リストの[拡張性]（拡張性]（拡張性。html）を参照）。 / Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -386,22 +386,22 @@
 </t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -420,22 +420,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -447,16 +447,16 @@
     <t>Extension.value[x].system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>保険医療機関コードの名前空間を識別するURIを指定。固定値。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicalOrganizationID</t>
@@ -477,7 +477,7 @@
     <t>保険医療機関番号７桁。半角数字で７桁固定。</t>
   </si>
   <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -496,7 +496,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -515,10 +515,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -863,7 +863,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -839,42 +839,42 @@
   <dimension ref="A1:AK14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="27.703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="233.2578125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="87.9765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -438,7 +438,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -508,7 +508,7 @@
     <t>Extension.value[x].assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -864,7 +864,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.1484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization-insuranceorganizationno.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
